--- a/data/trans_camb/IP2004-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP2004-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-0.9500915500656321</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.849185655317946</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2.284369069539486</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-0.1257799932984239</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.5875235042378767</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-0.4995162688848951</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-3.410245492193068</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-3.832028333614706</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-0.4195021303262015</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-2.902978943911542</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-1.262098526767734</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-2.386749710474573</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>1.420056383716237</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2.77488778220129</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>5.276926841389654</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>3.609178504331913</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>2.6046164257273</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>2.227985637497561</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.2958219017274508</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.2644036940003023</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0.8624185289423536</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.04748575798772905</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.2000187411176306</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.170057222476124</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.7451911706279897</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.8561559469684757</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.2043124694375709</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.8432846485224174</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.3591814446064551</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.6556339679410047</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>0.8350445303762402</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>1.936009690068083</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>3.523064539895919</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>3.190346069969779</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.35571457547795</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.367900886540573</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>-0.9732709397778871</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-1.81224646807832</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-2.59704442826758</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-3.693613530718128</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-1.784086492613614</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-2.754396396324135</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-3.194720858671322</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-4.160652034284108</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-5.907721158429561</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-6.781105644544481</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-3.74779008123277</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-4.662287843838629</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>1.341218234428724</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-0.2585089984120567</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.1098429867261681</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>-1.241433010231118</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.01552332107666153</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>-1.38404155336343</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>-0.430290149346874</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.8012073221673748</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.6050721707268891</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.8605562278919775</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.5448790461400062</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.8412220412710679</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.9010168658882449</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.8185844008765509</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.9745377945232117</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>1.725242833102062</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>1.35395074845044</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.3367408679011562</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.0890581222140861</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.1108717600004068</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-0.4103412194273228</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>-1.071924820711477</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.369436822809048</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.0620252054954115</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.3295444214758828</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-0.5921003089151349</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-0.3036134223622104</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-4.097754199807822</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-3.666217114506592</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-2.012159582804256</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-2.606330174201222</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-2.592047964304796</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-2.469614253649311</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>1.191362931147967</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.004996161346897</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.188623021796694</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.6491869570954765</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.7429861821765362</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>1.114520215750589</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>-0.5147786284234528</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.1774174618034607</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.0948403089358611</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.5038934493038392</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.4263502741279847</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.2186211760136361</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -912,14 +1025,17 @@
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
+      <c r="D20" s="6" t="n">
+        <v>-1</v>
+      </c>
       <c r="E20" s="6" t="inlineStr"/>
       <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.8650531824372094</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -929,14 +1045,17 @@
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
+      <c r="D21" s="6" t="n">
+        <v>3.075829275895808</v>
+      </c>
       <c r="E21" s="6" t="inlineStr"/>
       <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="n">
+        <v>1.901637981702358</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>2.242773857651474</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1068,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-0.5181863425241859</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>2.805972144532975</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-2.086059841725024</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-2.70876645065025</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-1.242962606205606</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0.1831626775603154</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1094,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-5.256792818601457</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-1.622923905918092</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-7.477013438817012</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-7.770841417599829</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-4.45866859463034</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-3.129117825868407</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1120,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>2.278556975052286</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>7.024034803337392</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>2.25357697955752</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.5550892875165564</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>1.420787040966597</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>2.761971886388852</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1146,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-0.2552913533634202</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>1.382399278970667</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.4635262002387156</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.6018927142405193</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.3939694552122507</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.05805524633917916</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1018,14 +1173,21 @@
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="D26" s="6" t="n">
+        <v>-0.6435819944553925</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.851962434760301</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.6490653865545901</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1036,13 +1198,18 @@
       </c>
       <c r="C27" s="6" t="inlineStr"/>
       <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="n">
+        <v>1.649957240408575</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.862652109428637</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>1.229283576392301</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>2.05479059084235</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1222,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-0.8694479433205945</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-0.4267902902440341</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-0.1815994948436216</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-1.878211093426838</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-0.538270615852077</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-1.115538707868439</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1248,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-2.273051857333789</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-1.979624722261078</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-1.766565693949914</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-3.185618771716232</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-1.589240285027824</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-2.200571866783937</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1274,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>0.3630001058717752</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>0.8671839224425347</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>1.289611866830974</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>-0.6930593994391737</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.4923278698733854</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>-0.1798115468038932</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1300,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.3453478199573025</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>-0.1695226234612801</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.06169925244838159</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-0.6381307420732815</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.197550710208873</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>-0.4094138849768839</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1326,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.700638478667014</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.5895678520588347</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.4810272942346404</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.8520644971832838</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.476207101772972</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.6503960269975724</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1352,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.218773828132757</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0.5833272660018169</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.5934978202247858</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>-0.2488060290501311</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.2436617652543624</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>-0.06693870489705608</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1380,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
